--- a/docentes/Santiago Hernández Mariana - Estadisticos 20221.xlsx
+++ b/docentes/Santiago Hernández Mariana - Estadisticos 20221.xlsx
@@ -67,6 +67,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>MOLINA</t>
   </si>
   <si>
@@ -79,7 +82,7 @@
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
+    <t>PLIEGO</t>
   </si>
   <si>
     <t>DE JESUS</t>
@@ -91,7 +94,7 @@
     <t>COLOHUA</t>
   </si>
   <si>
-    <t>PLIEGO</t>
+    <t>JAIRO YAIR</t>
   </si>
   <si>
     <t>VICTOR MANUEL</t>
@@ -104,9 +107,6 @@
   </si>
   <si>
     <t>NAHUM HIRAM</t>
-  </si>
-  <si>
-    <t>JAIRO YAIR</t>
   </si>
 </sst>
 </file>
@@ -688,7 +688,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920193</v>
+        <v>22330051920378</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
@@ -711,7 +711,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920390</v>
+        <v>22330051920193</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -734,7 +734,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920199</v>
+        <v>22330051920390</v>
       </c>
       <c r="B4" t="s">
         <v>18</v>
@@ -757,13 +757,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920200</v>
+        <v>22330051920199</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
         <v>28</v>
@@ -780,7 +780,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920378</v>
+        <v>22330051920200</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>

--- a/docentes/Santiago Hernández Mariana - Estadisticos 20221.xlsx
+++ b/docentes/Santiago Hernández Mariana - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="33">
   <si>
     <t>Mat</t>
   </si>
@@ -73,6 +73,9 @@
     <t>MOLINA</t>
   </si>
   <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
     <t>TETLA</t>
   </si>
   <si>
@@ -88,6 +91,9 @@
     <t>DE JESUS</t>
   </si>
   <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
@@ -98,6 +104,9 @@
   </si>
   <si>
     <t>VICTOR MANUEL</t>
+  </si>
+  <si>
+    <t>JOSUE GUSTAVO</t>
   </si>
   <si>
     <t>LUIS</t>
@@ -572,16 +581,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="E2">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>51.28</v>
+      </c>
+      <c r="H2">
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -637,16 +649,16 @@
         <v>17</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>56.41</v>
+        <v>51.28</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -656,7 +668,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -694,10 +706,10 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -717,10 +729,10 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -734,16 +746,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920390</v>
+        <v>22330051920356</v>
       </c>
       <c r="B4" t="s">
         <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -757,16 +769,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920199</v>
+        <v>22330051920390</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -780,16 +792,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920200</v>
+        <v>22330051920199</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -798,6 +810,29 @@
         <v>9</v>
       </c>
       <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>22330051920200</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Santiago Hernández Mariana - Estadisticos 20221.xlsx
+++ b/docentes/Santiago Hernández Mariana - Estadisticos 20221.xlsx
@@ -82,7 +82,7 @@
     <t>TZOMPOLE</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
+    <t>VASQUEZ</t>
   </si>
   <si>
     <t>PLIEGO</t>

--- a/docentes/Santiago Hernández Mariana - Estadisticos 20221.xlsx
+++ b/docentes/Santiago Hernández Mariana - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="38">
   <si>
     <t>Mat</t>
   </si>
@@ -67,10 +67,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>MOLINA</t>
+    <t>MARQUEZ</t>
   </si>
   <si>
     <t>RUIZ</t>
@@ -79,16 +82,22 @@
     <t>TETLA</t>
   </si>
   <si>
-    <t>TZOMPOLE</t>
+    <t>XOTLANIHUA</t>
   </si>
   <si>
     <t>VASQUEZ</t>
   </si>
   <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
     <t>PLIEGO</t>
   </si>
   <si>
-    <t>DE JESUS</t>
+    <t>TIZA</t>
   </si>
   <si>
     <t>ALFONSO</t>
@@ -100,10 +109,16 @@
     <t>COLOHUA</t>
   </si>
   <si>
+    <t>ARACELY</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
     <t>JAIRO YAIR</t>
   </si>
   <si>
-    <t>VICTOR MANUEL</t>
+    <t>CRISTIAN OSMAR</t>
   </si>
   <si>
     <t>JOSUE GUSTAVO</t>
@@ -112,7 +127,7 @@
     <t>LUIS</t>
   </si>
   <si>
-    <t>JOSE LEONARDO</t>
+    <t>ALEXANDER</t>
   </si>
   <si>
     <t>NAHUM HIRAM</t>
@@ -516,19 +531,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>56.41</v>
+        <v>69.23</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
@@ -581,19 +596,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>51.28</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
@@ -646,19 +661,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>51.28</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -668,7 +683,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -700,16 +715,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920378</v>
+        <v>22330051920190</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -723,16 +738,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920193</v>
+        <v>22330051920388</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -746,16 +761,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920356</v>
+        <v>22330051920378</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -769,16 +784,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920390</v>
+        <v>22330051920359</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -792,16 +807,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920199</v>
+        <v>22330051920356</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -815,24 +830,70 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
+        <v>22330051920390</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>22330051920201</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
         <v>22330051920200</v>
       </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7">
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Santiago Hernández Mariana - Estadisticos 20221.xlsx
+++ b/docentes/Santiago Hernández Mariana - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="43">
   <si>
     <t>Mat</t>
   </si>
@@ -73,61 +73,76 @@
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
     <t>MARQUEZ</t>
   </si>
   <si>
-    <t>RUIZ</t>
+    <t>PELLICO</t>
   </si>
   <si>
     <t>TETLA</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
     <t>VASQUEZ</t>
   </si>
   <si>
     <t>CIRUELO</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
     <t>ALVAREZ</t>
   </si>
   <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
     <t>TIZA</t>
   </si>
   <si>
-    <t>ALFONSO</t>
+    <t>TEQUIHUATLE</t>
   </si>
   <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
     <t>ARACELY</t>
   </si>
   <si>
+    <t>RICARDO ABEL</t>
+  </si>
+  <si>
+    <t>JAIRO YAIR</t>
+  </si>
+  <si>
+    <t>JOSUE GUSTAVO</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
     <t>ANGEL DE JESUS</t>
   </si>
   <si>
-    <t>JAIRO YAIR</t>
-  </si>
-  <si>
     <t>CRISTIAN OSMAR</t>
   </si>
   <si>
-    <t>JOSUE GUSTAVO</t>
+    <t>JESUS IVAN</t>
   </si>
   <si>
     <t>LUIS</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
   </si>
   <si>
     <t>NAHUM HIRAM</t>
@@ -683,7 +698,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -721,10 +736,10 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -738,16 +753,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920388</v>
+        <v>21330051920265</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -767,10 +782,10 @@
         <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -784,16 +799,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920359</v>
+        <v>22330051920356</v>
       </c>
       <c r="B5" t="s">
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -807,16 +822,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920356</v>
+        <v>22330051920201</v>
       </c>
       <c r="B6" t="s">
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -830,16 +845,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920390</v>
+        <v>22330051920388</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -848,21 +863,21 @@
         <v>9</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920201</v>
+        <v>22330051920359</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -871,29 +886,75 @@
         <v>9</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
+        <v>22330051920195</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920390</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
         <v>22330051920200</v>
       </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9">
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Santiago Hernández Mariana - Estadisticos 20221.xlsx
+++ b/docentes/Santiago Hernández Mariana - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="32">
   <si>
     <t>Mat</t>
   </si>
@@ -73,24 +73,12 @@
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
+    <t>ZEPAHUA</t>
   </si>
   <si>
     <t>PELLICO</t>
   </si>
   <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
     <t>CIRUELO</t>
   </si>
   <si>
@@ -100,24 +88,15 @@
     <t>PLIEGO</t>
   </si>
   <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
+    <t>XICALHUA</t>
   </si>
   <si>
     <t>ALVAREZ</t>
   </si>
   <si>
-    <t>TIZA</t>
-  </si>
-  <si>
     <t>TEQUIHUATLE</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
     <t>ARACELY</t>
   </si>
   <si>
@@ -127,25 +106,13 @@
     <t>JAIRO YAIR</t>
   </si>
   <si>
-    <t>JOSUE GUSTAVO</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
+    <t>YAIR</t>
   </si>
   <si>
     <t>ANGEL DE JESUS</t>
   </si>
   <si>
-    <t>CRISTIAN OSMAR</t>
-  </si>
-  <si>
     <t>JESUS IVAN</t>
-  </si>
-  <si>
-    <t>LUIS</t>
-  </si>
-  <si>
-    <t>NAHUM HIRAM</t>
   </si>
 </sst>
 </file>
@@ -679,16 +646,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>64.09999999999999</v>
+        <v>76.92</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -698,7 +665,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -736,10 +703,10 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -759,10 +726,10 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -782,10 +749,10 @@
         <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -799,16 +766,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920356</v>
+        <v>22330051920204</v>
       </c>
       <c r="B5" t="s">
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -822,16 +789,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920201</v>
+        <v>22330051920388</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -840,21 +807,21 @@
         <v>9</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920388</v>
+        <v>22330051920195</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -863,98 +830,6 @@
         <v>9</v>
       </c>
       <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920359</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920195</v>
-      </c>
-      <c r="B9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920390</v>
-      </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920200</v>
-      </c>
-      <c r="B11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Santiago Hernández Mariana - Estadisticos 20221.xlsx
+++ b/docentes/Santiago Hernández Mariana - Estadisticos 20221.xlsx
@@ -73,12 +73,12 @@
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
     <t>CIRUELO</t>
   </si>
   <si>
@@ -88,15 +88,15 @@
     <t>PLIEGO</t>
   </si>
   <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
     <t>XICALHUA</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
     <t>ARACELY</t>
   </si>
   <si>
@@ -106,13 +106,13 @@
     <t>JAIRO YAIR</t>
   </si>
   <si>
+    <t>JESUS IVAN</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
     <t>YAIR</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>JESUS IVAN</t>
   </si>
 </sst>
 </file>
@@ -766,7 +766,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920204</v>
+        <v>22330051920195</v>
       </c>
       <c r="B5" t="s">
         <v>18</v>
@@ -812,7 +812,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920195</v>
+        <v>22330051920204</v>
       </c>
       <c r="B7" t="s">
         <v>19</v>
